--- a/exemple-arborescence-prerempli.xlsx
+++ b/exemple-arborescence-prerempli.xlsx
@@ -287,7 +287,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>Code d'un enjeu (ex : E1) OU d'un indicateur (ex : I1). (obligatoire)</t>
+        <t>Code d'un enjeu (ex : E1). (obligatoire)</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -312,7 +312,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>Code d'un enjeu (ex : E1) OU d'un indicateur (ex : I1). (obligatoire)</t>
+        <t>Code d'un enjeu (ex : E1). (obligatoire)</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -2845,7 +2845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2856,14 +2856,14 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Espèces (TaxRef) rattachées à un enjeu ou à un indicateur, via le code de la cible.</t>
+          <t>Espèces (TaxRef) rattachées à un enjeu, via le code de la cible.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>cible (enjeu ou indicateur)</t>
+          <t>cible (enjeu)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -2910,43 +2910,13 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>I12</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>2840</v>
+        <v>117835</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Pandion haliaetus</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>117835</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Reynoutria japonica</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>I19</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>117835</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Reynoutria japonica</t>
         </is>
@@ -2968,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2979,14 +2949,14 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Habitats (HabRef) rattachés à un enjeu ou à un indicateur, via le code de la cible.</t>
+          <t>Habitats (HabRef) rattachés à un enjeu, via le code de la cible.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>cible (enjeu ou indicateur)</t>
+          <t>cible (enjeu)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3054,49 +3024,15 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Tourbières hautes actives</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Prairies de fauche de montagne</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>I17</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Prairies de fauche de montagne</t>
         </is>
